--- a/reports/pdf_change_20261002.xlsx
+++ b/reports/pdf_change_20261002.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,035억   ·   현금 18억(0.3%)      당일 2026-10-02  vs  전영업일 2026-10-01      매수 2종목  /  매도 4종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,330억      당일 2026-10-02  vs  전영업일 2026-10-01      매수 2종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>29</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1567885478</v>
+        <v>1556719649</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-43</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1509003761</v>
+        <v>-1498257262</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>24</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>2116203046</v>
+        <v>2101132326</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-34</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-984278200</v>
+        <v>-977268580</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>-12</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-603955384</v>
+        <v>-599654265</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>-8</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-324390099</v>
+        <v>-322079927</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,250억   ·   현금 22억(0.6%)      당일 2026-10-02  vs  전영업일 2026-10-01      매수 6종목  /  매도 5종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,475억      당일 2026-10-02  vs  전영업일 2026-10-01      매수 6종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
@@ -903,7 +903,7 @@
         <v>119</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1801760805</v>
+        <v>1801761150</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -917,14 +917,14 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>뉴로핏  (편출)</t>
+          <t>뉴로핏  (편출) ※</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-233</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-924909633</v>
+        <v>-924909810</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>50</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>703434866</v>
+        <v>703435000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>-82</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-707618865</v>
+        <v>-707619000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>32</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>728015861</v>
+        <v>728016000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>-70</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-939046320</v>
+        <v>-939046500</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>25</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>700819866</v>
+        <v>700820000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>-20</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-999975809</v>
+        <v>-999976000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>10</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>960227816</v>
+        <v>960228000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>-19</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-329908337</v>
+        <v>-329908400</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>10</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>676238871</v>
+        <v>676239000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,723억   ·   현금 44억(1.5%)      당일 2026-10-02  vs  전영업일 2026-10-01      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,868억      당일 2026-10-02  vs  전영업일 2026-10-01      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1168,7 +1168,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,988억   ·   현금 10억(0.5%)      당일 2026-10-02  vs  전영업일 2026-10-01      매수 2종목  /  매도 4종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,140억      당일 2026-10-02  vs  전영업일 2026-10-01      매수 2종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1264,7 +1264,7 @@
         <v>295</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>4632531987</v>
+        <v>4632531473</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>-342</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1344501031</v>
+        <v>-1344500882</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>211</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>2224192954</v>
+        <v>2224192707</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1322,14 +1322,14 @@
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>셀트리온제약  (편출)</t>
+          <t>셀트리온제약  (편출) ※</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-208</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-2860852483</v>
+        <v>-2860852166</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>-60</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-2070695771</v>
+        <v>-2070695541</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>-45</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-870731904</v>
+        <v>-870731807</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 308억   ·   현금 2억(0.5%)      당일 2026-10-02  vs  전영업일 2026-10-01      매수 2종목  /  매도 4종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 326억      당일 2026-10-02  vs  전영업일 2026-10-01      매수 2종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1497,11 +1497,11 @@
         <v>44</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>62062000</v>
+        <v>67298000</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>2.04%→2.24%</t>
+          <t>2.09%→2.30%</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
@@ -1518,11 +1518,11 @@
         <v>-41</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-34727000</v>
+        <v>-34870500</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>2.26%→2.15%</t>
+          <t>2.15%→2.04%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
@@ -1541,11 +1541,11 @@
         <v>35</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>62842500</v>
+        <v>63822500</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>4.87%→5.08%</t>
+          <t>4.69%→4.88%</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
@@ -1562,11 +1562,11 @@
         <v>-14</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-39543000</v>
+        <v>-41160000</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>2.29%→2.16%</t>
+          <t>2.26%→2.13%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
@@ -1590,11 +1590,11 @@
         <v>-7</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-30870000</v>
+        <v>-34692000</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>2.87%→2.77%</t>
+          <t>3.06%→2.95%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
@@ -1618,11 +1618,11 @@
         <v>-5</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-32375000</v>
+        <v>-32795000</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>1.37%→1.27%</t>
+          <t>1.32%→1.21%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
@@ -1634,7 +1634,7 @@
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 474억   ·   현금 143억(22.1%)      당일 2026-10-02  vs  전영업일 2026-10-01      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 509억      당일 2026-10-02  vs  전영업일 2026-10-01      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>

--- a/reports/pdf_change_20261002.xlsx
+++ b/reports/pdf_change_20261002.xlsx
@@ -1072,23 +1072,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>녹십자</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>960228000</v>
+        <v>676239000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>8.28%→8.23%</t>
+          <t>3.57%→3.68%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>286→296</t>
+          <t>178→188</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1116,23 +1116,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>녹십자</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>676239000</v>
+        <v>960228000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>3.57%→3.68%</t>
+          <t>8.28%→8.23%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>178→188</t>
+          <t>286→296</t>
         </is>
       </c>
       <c r="G19" s="17" t="n"/>

--- a/reports/pdf_change_20261002.xlsx
+++ b/reports/pdf_change_20261002.xlsx
@@ -1072,23 +1072,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>녹십자</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>676239000</v>
+        <v>960228000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>3.57%→3.68%</t>
+          <t>8.28%→8.23%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>178→188</t>
+          <t>286→296</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1116,23 +1116,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>녹십자</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>960228000</v>
+        <v>676239000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>8.28%→8.23%</t>
+          <t>3.57%→3.68%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>286→296</t>
+          <t>178→188</t>
         </is>
       </c>
       <c r="G19" s="17" t="n"/>
